--- a/ИД/Завзаказ/1269/КД/1269-3 Пульт керування намоткою/наличие  1269-3.xlsx
+++ b/ИД/Завзаказ/1269/КД/1269-3 Пульт керування намоткою/наличие  1269-3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Общие диски\04_ЗавЗакази\2026\1269_Юр-Пак\КД\1269-3 Пульт керування намоткою\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEA6134-895D-4598-B486-02C73A53F8B1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94ACE56-6D8F-44E5-B54C-CE529323944D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_FilterDatabase" localSheetId="0" hidden="1">'SR Групповая спецификация из'!$A$5:$J$6</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="OnQgIQuefymm4Wz1wn9GtwpgIuZi4BZimN8WMxMiqX8="/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="64">
   <si>
     <t/>
   </si>
@@ -208,6 +208,18 @@
   </si>
   <si>
     <t>TNSy5505574</t>
+  </si>
+  <si>
+    <t>Перемикач 22 мм 3 позиції, пружинне повернення</t>
+  </si>
+  <si>
+    <t>XA2ED53</t>
+  </si>
+  <si>
+    <t>Прибрати 24.02.2025</t>
+  </si>
+  <si>
+    <t>Додати 24.02.2025</t>
   </si>
 </sst>
 </file>
@@ -425,7 +437,7 @@
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -503,6 +515,9 @@
     </xf>
     <xf numFmtId="49" fontId="8" fillId="6" borderId="4" xfId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1265,26 +1280,50 @@
       <c r="G21" s="4"/>
     </row>
     <row r="22" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="28" t="s">
+        <v>62</v>
+      </c>
       <c r="C22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="4"/>
     </row>
     <row r="23" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C23" s="7"/>
-      <c r="E23" s="7"/>
+      <c r="B23" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>14</v>
+      </c>
       <c r="F23" s="7"/>
       <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C24" s="7"/>
-      <c r="E24" s="7"/>
+      <c r="B24" s="28" t="s">
+        <v>63</v>
+      </c>
       <c r="F24" s="7"/>
       <c r="G24" s="4"/>
     </row>
     <row r="25" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C25" s="7"/>
-      <c r="E25" s="7"/>
+      <c r="B25" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>14</v>
+      </c>
       <c r="F25" s="7"/>
       <c r="G25" s="4"/>
     </row>
